--- a/data/raw/2026/6月/旅游.xlsx
+++ b/data/raw/2026/6月/旅游.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="26860" windowHeight="11360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问卷数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -1258,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ24"/>
+  <dimension ref="A1:BZ34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.44230769230769" customWidth="1" style="3" min="1" max="1"/>
@@ -1729,7 +1729,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>旅行社工作人员</t>
+          <t>游客</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>浙江省外</t>
+          <t>浙江省内</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>华北地区（京、津、冀、晋、蒙）</t>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="BF2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="BG2" s="2" t="inlineStr">
@@ -1961,27 +1961,27 @@
       <c r="BL2" s="2" t="inlineStr"/>
       <c r="BM2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15 10:26:02</t>
+          <t>2026-06-27 17:21:22</t>
         </is>
       </c>
       <c r="BN2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15 10:26:02</t>
+          <t>2026-06-27 17:21:22</t>
         </is>
       </c>
       <c r="BO2" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/688849487a7c4563aa8fc3aa9919a60f.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c8ba7508fb8141bd890e91308a9f4b17.mp3</t>
         </is>
       </c>
       <c r="BP2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 分 7 秒 </t>
+          <t xml:space="preserve">1 分 20 秒 </t>
         </is>
       </c>
       <c r="BQ2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15 10:21:52</t>
+          <t>2026-06-27 17:20:00</t>
         </is>
       </c>
       <c r="BR2" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="BV2" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW2" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2058,36 +2058,40 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+          <t>华南地区（粤、桂、琼、港、澳、台）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -2102,12 +2106,12 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -2122,7 +2126,7 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -2210,12 +2214,12 @@
       <c r="AS3" s="2" t="inlineStr"/>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AV3" s="2" t="inlineStr">
@@ -2241,22 +2245,22 @@
       </c>
       <c r="BE3" s="2" t="inlineStr">
         <is>
-          <t>专业知识</t>
+          <t>故事性</t>
         </is>
       </c>
       <c r="BF3" s="2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG3" s="2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BG3" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH3" s="2" t="inlineStr">
         <is>
-          <t>会推荐</t>
+          <t>可能会推荐</t>
         </is>
       </c>
       <c r="BI3" s="2" t="inlineStr"/>
@@ -2265,27 +2269,27 @@
       <c r="BL3" s="2" t="inlineStr"/>
       <c r="BM3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 15:06:14</t>
+          <t>2026-06-27 17:19:17</t>
         </is>
       </c>
       <c r="BN3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 15:06:14</t>
+          <t>2026-06-27 17:19:17</t>
         </is>
       </c>
       <c r="BO3" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4b6b1707600b4d6da18f39e4e02b0aec.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/6e8945e2750b44fd953c4f1a7fcfdcf9.mp3</t>
         </is>
       </c>
       <c r="BP3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 34 秒 </t>
+          <t xml:space="preserve">1 分 51 秒 </t>
         </is>
       </c>
       <c r="BQ3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 15:04:37</t>
+          <t>2026-06-27 17:17:23</t>
         </is>
       </c>
       <c r="BR3" s="2" t="inlineStr">
@@ -2310,7 +2314,7 @@
       </c>
       <c r="BV3" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW3" s="2" t="inlineStr">
@@ -2337,7 +2341,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2376,12 +2380,12 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
@@ -2545,7 +2549,7 @@
       </c>
       <c r="BE4" s="2" t="inlineStr">
         <is>
-          <t>专业知识</t>
+          <t>故事性</t>
         </is>
       </c>
       <c r="BF4" s="2" t="inlineStr">
@@ -2569,27 +2573,27 @@
       <c r="BL4" s="2" t="inlineStr"/>
       <c r="BM4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 15:04:13</t>
+          <t>2026-06-27 17:16:35</t>
         </is>
       </c>
       <c r="BN4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 15:04:13</t>
+          <t>2026-06-27 17:16:35</t>
         </is>
       </c>
       <c r="BO4" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ac25982e2a7d49e8b52d0d034d9f5291.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/abeaa037cb934229826e56fa2e3a22b8.mp3</t>
         </is>
       </c>
       <c r="BP4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 20 秒 </t>
+          <t xml:space="preserve">1 分 32 秒 </t>
         </is>
       </c>
       <c r="BQ4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 15:02:51</t>
+          <t>2026-06-27 17:15:00</t>
         </is>
       </c>
       <c r="BR4" s="2" t="inlineStr">
@@ -2614,7 +2618,7 @@
       </c>
       <c r="BV4" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW4" s="2" t="inlineStr">
@@ -2641,7 +2645,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2666,26 +2670,26 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+          <t>西南地区（渝、川、贵、云、藏）</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
@@ -2849,22 +2853,22 @@
       </c>
       <c r="BE5" s="2" t="inlineStr">
         <is>
-          <t>专业知识</t>
+          <t>趣味性</t>
         </is>
       </c>
       <c r="BF5" s="2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG5" s="2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BG5" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH5" s="2" t="inlineStr">
         <is>
-          <t>会推荐</t>
+          <t>可能会推荐</t>
         </is>
       </c>
       <c r="BI5" s="2" t="inlineStr"/>
@@ -2873,27 +2877,27 @@
       <c r="BL5" s="2" t="inlineStr"/>
       <c r="BM5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:51:36</t>
+          <t>2026-06-27 17:14:13</t>
         </is>
       </c>
       <c r="BN5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:51:36</t>
+          <t>2026-06-27 17:14:13</t>
         </is>
       </c>
       <c r="BO5" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/60378736b519470fa0370760081b0179.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/9d5a8d615b5244c6a5d0084ee55b8067.mp3</t>
         </is>
       </c>
       <c r="BP5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 35 秒 </t>
+          <t xml:space="preserve">1 分 46 秒 </t>
         </is>
       </c>
       <c r="BQ5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:49:59</t>
+          <t>2026-06-27 17:12:24</t>
         </is>
       </c>
       <c r="BR5" s="2" t="inlineStr">
@@ -2918,7 +2922,7 @@
       </c>
       <c r="BV5" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW5" s="2" t="inlineStr">
@@ -2945,7 +2949,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2984,12 +2988,12 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
@@ -3153,7 +3157,7 @@
       </c>
       <c r="BE6" s="2" t="inlineStr">
         <is>
-          <t>专业知识</t>
+          <t>故事性</t>
         </is>
       </c>
       <c r="BF6" s="2" t="inlineStr">
@@ -3177,27 +3181,27 @@
       <c r="BL6" s="2" t="inlineStr"/>
       <c r="BM6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:48:39</t>
+          <t>2026-06-27 17:12:06</t>
         </is>
       </c>
       <c r="BN6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:48:39</t>
+          <t>2026-06-27 17:12:06</t>
         </is>
       </c>
       <c r="BO6" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7aab0221f58f44e489a3d8437eb79f0f.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ac33a712f2fd4fed99720d955322f990.mp3</t>
         </is>
       </c>
       <c r="BP6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 11 秒 </t>
+          <t xml:space="preserve">2 分 6 秒 </t>
         </is>
       </c>
       <c r="BQ6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:46:25</t>
+          <t>2026-06-27 17:09:57</t>
         </is>
       </c>
       <c r="BR6" s="2" t="inlineStr">
@@ -3222,7 +3226,7 @@
       </c>
       <c r="BV6" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW6" s="2" t="inlineStr">
@@ -3249,7 +3253,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3269,12 +3273,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3288,12 +3292,12 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
@@ -3318,12 +3322,12 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3338,12 +3342,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
@@ -3358,7 +3362,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -3447,22 +3451,14 @@
       <c r="BB7" s="2" t="inlineStr"/>
       <c r="BC7" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="BD7" s="2" t="inlineStr">
-        <is>
-          <t>人工讲解导览</t>
-        </is>
-      </c>
-      <c r="BE7" s="2" t="inlineStr">
-        <is>
-          <t>专业知识</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr"/>
       <c r="BF7" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="BG7" s="2" t="inlineStr">
@@ -3481,27 +3477,27 @@
       <c r="BL7" s="2" t="inlineStr"/>
       <c r="BM7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:42:02</t>
+          <t>2026-06-27 17:09:38</t>
         </is>
       </c>
       <c r="BN7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:42:02</t>
+          <t>2026-06-27 17:09:38</t>
         </is>
       </c>
       <c r="BO7" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b613c77d706547159084e32c857eb61a.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/426fc307dc5d47128bd49d3c106866a8.mp3</t>
         </is>
       </c>
       <c r="BP7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 15 秒 </t>
+          <t xml:space="preserve">1 分 51 秒 </t>
         </is>
       </c>
       <c r="BQ7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:39:44</t>
+          <t>2026-06-27 17:07:43</t>
         </is>
       </c>
       <c r="BR7" s="2" t="inlineStr">
@@ -3526,7 +3522,7 @@
       </c>
       <c r="BV7" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW7" s="2" t="inlineStr">
@@ -3553,7 +3549,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3563,7 +3559,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>旅行社工作人员</t>
+          <t>游客</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3573,7 +3569,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3583,12 +3579,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+          <t>华中地区（豫、鄂、湘）</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -3597,7 +3593,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,11 +3751,19 @@
       <c r="BB8" s="2" t="inlineStr"/>
       <c r="BC8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="BD8" s="2" t="inlineStr"/>
-      <c r="BE8" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD8" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE8" s="2" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
       <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -3777,27 +3785,27 @@
       <c r="BL8" s="2" t="inlineStr"/>
       <c r="BM8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11 13:58:15</t>
+          <t>2026-06-27 17:03:48</t>
         </is>
       </c>
       <c r="BN8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11 13:58:15</t>
+          <t>2026-06-27 17:03:48</t>
         </is>
       </c>
       <c r="BO8" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/6fa8f1c92ca142e7be7ffbbb3d81f458.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/18be09daad30445f87e6d2dda194aae3.mp3</t>
         </is>
       </c>
       <c r="BP8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 20 秒 </t>
+          <t xml:space="preserve">1 分 43 秒 </t>
         </is>
       </c>
       <c r="BQ8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11 13:55:51</t>
+          <t>2026-06-27 17:02:02</t>
         </is>
       </c>
       <c r="BR8" s="2" t="inlineStr">
@@ -3822,7 +3830,7 @@
       </c>
       <c r="BV8" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW8" s="2" t="inlineStr">
@@ -3849,7 +3857,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3874,7 +3882,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4026,12 +4034,12 @@
       <c r="AS9" s="2" t="inlineStr"/>
       <c r="AT9" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AU9" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AV9" s="2" t="inlineStr">
@@ -4062,7 +4070,7 @@
       </c>
       <c r="BF9" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="BG9" s="2" t="inlineStr">
@@ -4081,27 +4089,27 @@
       <c r="BL9" s="2" t="inlineStr"/>
       <c r="BM9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:31:20</t>
+          <t>2026-06-27 17:01:48</t>
         </is>
       </c>
       <c r="BN9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:31:20</t>
+          <t>2026-06-27 17:01:48</t>
         </is>
       </c>
       <c r="BO9" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c708bb5d4fc2411d84b19bce38caf78e.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/915ebff326dd4ce3adebfac252aa297c.mp3</t>
         </is>
       </c>
       <c r="BP9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 43 秒 </t>
+          <t xml:space="preserve">1 分 37 秒 </t>
         </is>
       </c>
       <c r="BQ9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:29:34</t>
+          <t>2026-06-27 17:00:08</t>
         </is>
       </c>
       <c r="BR9" s="2" t="inlineStr">
@@ -4126,7 +4134,7 @@
       </c>
       <c r="BV9" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW9" s="2" t="inlineStr">
@@ -4153,7 +4161,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4173,22 +4181,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+          <t>华南地区（粤、桂、琼、港、澳、台）</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -4197,7 +4205,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
@@ -4361,7 +4373,7 @@
       </c>
       <c r="BE10" s="2" t="inlineStr">
         <is>
-          <t>故事性</t>
+          <t>专业知识</t>
         </is>
       </c>
       <c r="BF10" s="2" t="inlineStr">
@@ -4385,27 +4397,27 @@
       <c r="BL10" s="2" t="inlineStr"/>
       <c r="BM10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:25:08</t>
+          <t>2026-06-27 16:59:12</t>
         </is>
       </c>
       <c r="BN10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:25:08</t>
+          <t>2026-06-27 16:59:12</t>
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/67439ceb4fa84c81b9c5158dc36c3977.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/f3959074cb35474bb732d233260d9403.mp3</t>
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 43 秒 </t>
+          <t xml:space="preserve">2 分 36 秒 </t>
         </is>
       </c>
       <c r="BQ10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:23:22</t>
+          <t>2026-06-27 16:56:32</t>
         </is>
       </c>
       <c r="BR10" s="2" t="inlineStr">
@@ -4430,7 +4442,7 @@
       </c>
       <c r="BV10" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW10" s="2" t="inlineStr">
@@ -4457,7 +4469,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -4467,22 +4479,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>游客</t>
+          <t>旅行社工作人员</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>首次</t>
+          <t>2次及以上</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4689,27 +4701,27 @@
       <c r="BL11" s="2" t="inlineStr"/>
       <c r="BM11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:18:03</t>
+          <t>2026-06-27 16:55:38</t>
         </is>
       </c>
       <c r="BN11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:18:03</t>
+          <t>2026-06-27 16:55:38</t>
         </is>
       </c>
       <c r="BO11" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b6e8b103655e411f99f680cd540373c7.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/98bb874799794a0a96f6f36feb8298a9.mp3</t>
         </is>
       </c>
       <c r="BP11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 53 秒 </t>
+          <t xml:space="preserve">1 分 57 秒 </t>
         </is>
       </c>
       <c r="BQ11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:16:07</t>
+          <t>2026-06-27 16:53:38</t>
         </is>
       </c>
       <c r="BR11" s="2" t="inlineStr">
@@ -4734,7 +4746,7 @@
       </c>
       <c r="BV11" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW11" s="2" t="inlineStr">
@@ -4761,7 +4773,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4771,7 +4783,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>游客</t>
+          <t>旅行社工作人员</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4781,22 +4793,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+          <t>华北地区（京、津、冀、晋、蒙）</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -4820,12 +4832,12 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -4969,12 +4981,12 @@
       </c>
       <c r="BE12" s="2" t="inlineStr">
         <is>
-          <t>故事性</t>
+          <t>专业知识</t>
         </is>
       </c>
       <c r="BF12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="BG12" s="2" t="inlineStr">
@@ -4993,27 +5005,27 @@
       <c r="BL12" s="2" t="inlineStr"/>
       <c r="BM12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:40:01</t>
+          <t>2026-06-15 10:26:02</t>
         </is>
       </c>
       <c r="BN12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:40:01</t>
+          <t>2026-06-15 10:26:02</t>
         </is>
       </c>
       <c r="BO12" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4e8e113158964b958db9709388aa6a1d.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/688849487a7c4563aa8fc3aa9919a60f.mp3</t>
         </is>
       </c>
       <c r="BP12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 52 秒 </t>
+          <t xml:space="preserve">4 分 7 秒 </t>
         </is>
       </c>
       <c r="BQ12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:38:06</t>
+          <t>2026-06-15 10:21:52</t>
         </is>
       </c>
       <c r="BR12" s="2" t="inlineStr">
@@ -5038,7 +5050,7 @@
       </c>
       <c r="BV12" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW12" s="2" t="inlineStr">
@@ -5065,7 +5077,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -5085,7 +5097,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5104,12 +5116,12 @@
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
@@ -5278,7 +5290,7 @@
       </c>
       <c r="BF13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="BG13" s="2" t="inlineStr">
@@ -5297,27 +5309,27 @@
       <c r="BL13" s="2" t="inlineStr"/>
       <c r="BM13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:36:01</t>
+          <t>2026-06-12 15:06:14</t>
         </is>
       </c>
       <c r="BN13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:36:01</t>
+          <t>2026-06-12 15:06:14</t>
         </is>
       </c>
       <c r="BO13" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/867f99d38a12471cb62d79ed221cab5c.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4b6b1707600b4d6da18f39e4e02b0aec.mp3</t>
         </is>
       </c>
       <c r="BP13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 10 秒 </t>
+          <t xml:space="preserve">1 分 34 秒 </t>
         </is>
       </c>
       <c r="BQ13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:33:47</t>
+          <t>2026-06-12 15:04:37</t>
         </is>
       </c>
       <c r="BR13" s="2" t="inlineStr">
@@ -5342,7 +5354,7 @@
       </c>
       <c r="BV13" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW13" s="2" t="inlineStr">
@@ -5369,7 +5381,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -5389,12 +5401,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5408,12 +5420,12 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
@@ -5601,27 +5613,27 @@
       <c r="BL14" s="2" t="inlineStr"/>
       <c r="BM14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:29:55</t>
+          <t>2026-06-12 15:04:13</t>
         </is>
       </c>
       <c r="BN14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:29:55</t>
+          <t>2026-06-12 15:04:13</t>
         </is>
       </c>
       <c r="BO14" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ce654b0e29e243c2a973d4f2da16328c.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ac25982e2a7d49e8b52d0d034d9f5291.mp3</t>
         </is>
       </c>
       <c r="BP14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 2 秒 </t>
+          <t xml:space="preserve">1 分 20 秒 </t>
         </is>
       </c>
       <c r="BQ14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:27:50</t>
+          <t>2026-06-12 15:02:51</t>
         </is>
       </c>
       <c r="BR14" s="2" t="inlineStr">
@@ -5646,7 +5658,7 @@
       </c>
       <c r="BV14" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW14" s="2" t="inlineStr">
@@ -5673,7 +5685,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -5683,7 +5695,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>旅行社工作人员</t>
+          <t>游客</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -5693,12 +5705,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5712,12 +5724,12 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
@@ -5905,27 +5917,27 @@
       <c r="BL15" s="2" t="inlineStr"/>
       <c r="BM15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:21:56</t>
+          <t>2026-06-12 14:51:36</t>
         </is>
       </c>
       <c r="BN15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:21:56</t>
+          <t>2026-06-12 14:51:36</t>
         </is>
       </c>
       <c r="BO15" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/621680565b774e0680af6c501e9b88f5.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/60378736b519470fa0370760081b0179.mp3</t>
         </is>
       </c>
       <c r="BP15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 51 秒 </t>
+          <t xml:space="preserve">1 分 35 秒 </t>
         </is>
       </c>
       <c r="BQ15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:20:02</t>
+          <t>2026-06-12 14:49:59</t>
         </is>
       </c>
       <c r="BR15" s="2" t="inlineStr">
@@ -5950,7 +5962,7 @@
       </c>
       <c r="BV15" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW15" s="2" t="inlineStr">
@@ -5977,7 +5989,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6002,7 +6014,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6016,17 +6028,17 @@
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -6046,7 +6058,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -6154,12 +6166,12 @@
       <c r="AS16" s="2" t="inlineStr"/>
       <c r="AT16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AU16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AV16" s="2" t="inlineStr">
@@ -6185,7 +6197,7 @@
       </c>
       <c r="BE16" s="2" t="inlineStr">
         <is>
-          <t>故事性</t>
+          <t>专业知识</t>
         </is>
       </c>
       <c r="BF16" s="2" t="inlineStr">
@@ -6209,27 +6221,27 @@
       <c r="BL16" s="2" t="inlineStr"/>
       <c r="BM16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:17:56</t>
+          <t>2026-06-12 14:48:39</t>
         </is>
       </c>
       <c r="BN16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:17:56</t>
+          <t>2026-06-12 14:48:39</t>
         </is>
       </c>
       <c r="BO16" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/e4660a6e7b1b4fc7ae2a637e5cfa8292.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7aab0221f58f44e489a3d8437eb79f0f.mp3</t>
         </is>
       </c>
       <c r="BP16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 </t>
+          <t xml:space="preserve">2 分 11 秒 </t>
         </is>
       </c>
       <c r="BQ16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:15:53</t>
+          <t>2026-06-12 14:46:25</t>
         </is>
       </c>
       <c r="BR16" s="2" t="inlineStr">
@@ -6254,7 +6266,7 @@
       </c>
       <c r="BV16" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW16" s="2" t="inlineStr">
@@ -6281,7 +6293,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -6301,31 +6313,31 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>浙江省外</t>
+          <t>浙江省内</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>西南地区（渝、川、贵、云、藏）</t>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
@@ -6513,27 +6525,27 @@
       <c r="BL17" s="2" t="inlineStr"/>
       <c r="BM17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:10:53</t>
+          <t>2026-06-12 14:42:02</t>
         </is>
       </c>
       <c r="BN17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:10:53</t>
+          <t>2026-06-12 14:42:02</t>
         </is>
       </c>
       <c r="BO17" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/bda17dbf386f421389ed6370f811d70d.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b613c77d706547159084e32c857eb61a.mp3</t>
         </is>
       </c>
       <c r="BP17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 4 秒 </t>
+          <t xml:space="preserve">2 分 15 秒 </t>
         </is>
       </c>
       <c r="BQ17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:07:46</t>
+          <t>2026-06-12 14:39:44</t>
         </is>
       </c>
       <c r="BR17" s="2" t="inlineStr">
@@ -6558,7 +6570,7 @@
       </c>
       <c r="BV17" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW17" s="2" t="inlineStr">
@@ -6585,7 +6597,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -6595,7 +6607,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>游客</t>
+          <t>旅行社工作人员</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -6783,19 +6795,11 @@
       <c r="BB18" s="2" t="inlineStr"/>
       <c r="BC18" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="BD18" s="2" t="inlineStr">
-        <is>
-          <t>人工讲解导览</t>
-        </is>
-      </c>
-      <c r="BE18" s="2" t="inlineStr">
-        <is>
-          <t>专业知识</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr"/>
       <c r="BF18" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -6817,27 +6821,27 @@
       <c r="BL18" s="2" t="inlineStr"/>
       <c r="BM18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:00:43</t>
+          <t>2026-06-11 13:58:15</t>
         </is>
       </c>
       <c r="BN18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:00:43</t>
+          <t>2026-06-11 13:58:15</t>
         </is>
       </c>
       <c r="BO18" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/86b9a3463f6b40988e95832b993002f4.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/6fa8f1c92ca142e7be7ffbbb3d81f458.mp3</t>
         </is>
       </c>
       <c r="BP18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 26 秒 </t>
+          <t xml:space="preserve">2 分 20 秒 </t>
         </is>
       </c>
       <c r="BQ18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 14:58:14</t>
+          <t>2026-06-11 13:55:51</t>
         </is>
       </c>
       <c r="BR18" s="2" t="inlineStr">
@@ -6862,7 +6866,7 @@
       </c>
       <c r="BV18" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW18" s="2" t="inlineStr">
@@ -6889,7 +6893,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -6909,7 +6913,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -7066,12 +7070,12 @@
       <c r="AS19" s="2" t="inlineStr"/>
       <c r="AT19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AU19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AV19" s="2" t="inlineStr">
@@ -7121,27 +7125,27 @@
       <c r="BL19" s="2" t="inlineStr"/>
       <c r="BM19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 14:57:25</t>
+          <t>2026-06-10 16:31:20</t>
         </is>
       </c>
       <c r="BN19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 14:57:25</t>
+          <t>2026-06-10 16:31:20</t>
         </is>
       </c>
       <c r="BO19" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/a20165306c164ddfa57672b5816d8b5c.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c708bb5d4fc2411d84b19bce38caf78e.mp3</t>
         </is>
       </c>
       <c r="BP19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 12 秒 </t>
+          <t xml:space="preserve">1 分 43 秒 </t>
         </is>
       </c>
       <c r="BQ19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 14:55:09</t>
+          <t>2026-06-10 16:29:34</t>
         </is>
       </c>
       <c r="BR19" s="2" t="inlineStr">
@@ -7166,7 +7170,7 @@
       </c>
       <c r="BV19" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW19" s="2" t="inlineStr">
@@ -7193,7 +7197,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -7208,7 +7212,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2次及以上</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -7218,7 +7222,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7231,12 +7235,12 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
@@ -7272,12 +7276,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -7332,12 +7336,12 @@
       </c>
       <c r="AF20" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AG20" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AH20" s="2" t="inlineStr">
@@ -7391,11 +7395,19 @@
       <c r="BB20" s="2" t="inlineStr"/>
       <c r="BC20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="BD20" s="2" t="inlineStr"/>
-      <c r="BE20" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD20" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE20" s="2" t="inlineStr">
+        <is>
+          <t>故事性</t>
+        </is>
+      </c>
       <c r="BF20" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -7417,27 +7429,27 @@
       <c r="BL20" s="2" t="inlineStr"/>
       <c r="BM20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 16:40:49</t>
+          <t>2026-06-10 16:25:08</t>
         </is>
       </c>
       <c r="BN20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 16:40:49</t>
+          <t>2026-06-10 16:25:08</t>
         </is>
       </c>
       <c r="BO20" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/53b5194f2d7c4bc0ba8dd14e9afe4caa.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/67439ceb4fa84c81b9c5158dc36c3977.mp3</t>
         </is>
       </c>
       <c r="BP20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 49 秒 </t>
+          <t xml:space="preserve">1 分 43 秒 </t>
         </is>
       </c>
       <c r="BQ20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 16:38:57</t>
+          <t>2026-06-10 16:23:22</t>
         </is>
       </c>
       <c r="BR20" s="2" t="inlineStr">
@@ -7462,7 +7474,7 @@
       </c>
       <c r="BV20" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体博览城</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW20" s="2" t="inlineStr">
@@ -7489,7 +7501,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -7509,12 +7521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7527,12 +7539,12 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
@@ -7568,12 +7580,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -7628,12 +7640,12 @@
       </c>
       <c r="AF21" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AG21" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AH21" s="2" t="inlineStr">
@@ -7687,11 +7699,19 @@
       <c r="BB21" s="2" t="inlineStr"/>
       <c r="BC21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="BD21" s="2" t="inlineStr"/>
-      <c r="BE21" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD21" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE21" s="2" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
       <c r="BF21" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -7713,27 +7733,27 @@
       <c r="BL21" s="2" t="inlineStr"/>
       <c r="BM21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:36:31</t>
+          <t>2026-06-10 16:18:03</t>
         </is>
       </c>
       <c r="BN21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:36:31</t>
+          <t>2026-06-10 16:18:03</t>
         </is>
       </c>
       <c r="BO21" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/d5ec9c3050de4f11b78de3480848d88f.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b6e8b103655e411f99f680cd540373c7.mp3</t>
         </is>
       </c>
       <c r="BP21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 23 秒 </t>
+          <t xml:space="preserve">1 分 53 秒 </t>
         </is>
       </c>
       <c r="BQ21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:35:05</t>
+          <t>2026-06-10 16:16:07</t>
         </is>
       </c>
       <c r="BR21" s="2" t="inlineStr">
@@ -7758,7 +7778,7 @@
       </c>
       <c r="BV21" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体中心国博壁球馆</t>
+          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW21" s="2" t="inlineStr">
@@ -7785,7 +7805,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -7800,7 +7820,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2次及以上</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -7810,7 +7830,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7823,18 +7843,18 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -7854,7 +7874,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -7864,12 +7884,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -7924,12 +7944,12 @@
       </c>
       <c r="AF22" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AG22" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AH22" s="2" t="inlineStr">
@@ -7962,12 +7982,12 @@
       <c r="AS22" s="2" t="inlineStr"/>
       <c r="AT22" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AU22" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AV22" s="2" t="inlineStr">
@@ -7983,14 +8003,22 @@
       <c r="BB22" s="2" t="inlineStr"/>
       <c r="BC22" s="2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD22" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE22" s="2" t="inlineStr">
+        <is>
+          <t>故事性</t>
+        </is>
+      </c>
+      <c r="BF22" s="2" t="inlineStr">
+        <is>
           <t>否</t>
-        </is>
-      </c>
-      <c r="BD22" s="2" t="inlineStr"/>
-      <c r="BE22" s="2" t="inlineStr"/>
-      <c r="BF22" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
       <c r="BG22" s="2" t="inlineStr">
@@ -8009,27 +8037,27 @@
       <c r="BL22" s="2" t="inlineStr"/>
       <c r="BM22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:33:55</t>
+          <t>2026-06-10 15:40:01</t>
         </is>
       </c>
       <c r="BN22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:33:55</t>
+          <t>2026-06-10 15:40:01</t>
         </is>
       </c>
       <c r="BO22" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/384cba67e55b4a6ba45ed7d200dd5945.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4e8e113158964b958db9709388aa6a1d.mp3</t>
         </is>
       </c>
       <c r="BP22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 38 秒 </t>
+          <t xml:space="preserve">1 分 52 秒 </t>
         </is>
       </c>
       <c r="BQ22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:32:15</t>
+          <t>2026-06-10 15:38:06</t>
         </is>
       </c>
       <c r="BR22" s="2" t="inlineStr">
@@ -8054,7 +8082,7 @@
       </c>
       <c r="BV22" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW22" s="2" t="inlineStr">
@@ -8081,7 +8109,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -8106,7 +8134,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8119,12 +8147,12 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
@@ -8160,12 +8188,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -8279,11 +8307,19 @@
       <c r="BB23" s="2" t="inlineStr"/>
       <c r="BC23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="BD23" s="2" t="inlineStr"/>
-      <c r="BE23" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD23" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE23" s="2" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
       <c r="BF23" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -8305,27 +8341,27 @@
       <c r="BL23" s="2" t="inlineStr"/>
       <c r="BM23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 12:30:06</t>
+          <t>2026-06-10 15:36:01</t>
         </is>
       </c>
       <c r="BN23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 12:30:06</t>
+          <t>2026-06-10 15:36:01</t>
         </is>
       </c>
       <c r="BO23" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b5f5c6a9b4f14082913aafc79904c9cd.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/867f99d38a12471cb62d79ed221cab5c.mp3</t>
         </is>
       </c>
       <c r="BP23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 51 秒 </t>
+          <t xml:space="preserve">2 分 10 秒 </t>
         </is>
       </c>
       <c r="BQ23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 12:28:12</t>
+          <t>2026-06-10 15:33:47</t>
         </is>
       </c>
       <c r="BR23" s="2" t="inlineStr">
@@ -8350,7 +8386,7 @@
       </c>
       <c r="BV23" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW23" s="2" t="inlineStr">
@@ -8377,7 +8413,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -8392,7 +8428,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2次及以上</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8415,12 +8451,12 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
@@ -8446,7 +8482,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -8456,12 +8492,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -8516,12 +8552,12 @@
       </c>
       <c r="AF24" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AG24" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AH24" s="2" t="inlineStr">
@@ -8554,12 +8590,12 @@
       <c r="AS24" s="2" t="inlineStr"/>
       <c r="AT24" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AU24" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AV24" s="2" t="inlineStr">
@@ -8575,14 +8611,22 @@
       <c r="BB24" s="2" t="inlineStr"/>
       <c r="BC24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="BD24" s="2" t="inlineStr"/>
-      <c r="BE24" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD24" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE24" s="2" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
       <c r="BF24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="BG24" s="2" t="inlineStr">
@@ -8595,80 +8639,3080 @@
           <t>会推荐</t>
         </is>
       </c>
-      <c r="BI24" s="2" t="inlineStr">
-        <is>
-          <t>空中花园标识标牌太少</t>
-        </is>
-      </c>
+      <c r="BI24" s="2" t="inlineStr"/>
       <c r="BJ24" s="2" t="inlineStr"/>
       <c r="BK24" s="2" t="inlineStr"/>
       <c r="BL24" s="2" t="inlineStr"/>
       <c r="BM24" s="2" t="inlineStr">
         <is>
+          <t>2026-06-10 15:29:55</t>
+        </is>
+      </c>
+      <c r="BN24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:29:55</t>
+        </is>
+      </c>
+      <c r="BO24" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ce654b0e29e243c2a973d4f2da16328c.mp3</t>
+        </is>
+      </c>
+      <c r="BP24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 2 秒 </t>
+        </is>
+      </c>
+      <c r="BQ24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:27:50</t>
+        </is>
+      </c>
+      <c r="BR24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT24" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV24" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW24" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX24" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY24" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ24" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>旅行社工作人员</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+      <c r="AK25" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL25" s="2" t="inlineStr"/>
+      <c r="AM25" s="2" t="inlineStr"/>
+      <c r="AN25" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO25" s="2" t="inlineStr"/>
+      <c r="AP25" s="2" t="inlineStr"/>
+      <c r="AQ25" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR25" s="2" t="inlineStr"/>
+      <c r="AS25" s="2" t="inlineStr"/>
+      <c r="AT25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW25" s="2" t="inlineStr"/>
+      <c r="AX25" s="2" t="inlineStr"/>
+      <c r="AY25" s="2" t="inlineStr"/>
+      <c r="AZ25" s="2" t="inlineStr"/>
+      <c r="BA25" s="2" t="inlineStr"/>
+      <c r="BB25" s="2" t="inlineStr"/>
+      <c r="BC25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD25" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE25" s="2" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH25" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BJ25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr"/>
+      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BM25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:21:56</t>
+        </is>
+      </c>
+      <c r="BN25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:21:56</t>
+        </is>
+      </c>
+      <c r="BO25" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/621680565b774e0680af6c501e9b88f5.mp3</t>
+        </is>
+      </c>
+      <c r="BP25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 51 秒 </t>
+        </is>
+      </c>
+      <c r="BQ25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:20:02</t>
+        </is>
+      </c>
+      <c r="BR25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT25" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV25" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW25" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX25" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY25" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ25" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="inlineStr"/>
+      <c r="AM26" s="2" t="inlineStr"/>
+      <c r="AN26" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO26" s="2" t="inlineStr"/>
+      <c r="AP26" s="2" t="inlineStr"/>
+      <c r="AQ26" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR26" s="2" t="inlineStr"/>
+      <c r="AS26" s="2" t="inlineStr"/>
+      <c r="AT26" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AU26" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW26" s="2" t="inlineStr"/>
+      <c r="AX26" s="2" t="inlineStr"/>
+      <c r="AY26" s="2" t="inlineStr"/>
+      <c r="AZ26" s="2" t="inlineStr"/>
+      <c r="BA26" s="2" t="inlineStr"/>
+      <c r="BB26" s="2" t="inlineStr"/>
+      <c r="BC26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD26" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE26" s="2" t="inlineStr">
+        <is>
+          <t>故事性</t>
+        </is>
+      </c>
+      <c r="BF26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH26" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr"/>
+      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BM26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:17:56</t>
+        </is>
+      </c>
+      <c r="BN26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:17:56</t>
+        </is>
+      </c>
+      <c r="BO26" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/e4660a6e7b1b4fc7ae2a637e5cfa8292.mp3</t>
+        </is>
+      </c>
+      <c r="BP26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 </t>
+        </is>
+      </c>
+      <c r="BQ26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:15:53</t>
+        </is>
+      </c>
+      <c r="BR26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT26" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV26" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW26" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX26" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY26" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ26" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>46-55岁</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>浙江省外</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>西南地区（渝、川、贵、云、藏）</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL27" s="2" t="inlineStr"/>
+      <c r="AM27" s="2" t="inlineStr"/>
+      <c r="AN27" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO27" s="2" t="inlineStr"/>
+      <c r="AP27" s="2" t="inlineStr"/>
+      <c r="AQ27" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR27" s="2" t="inlineStr"/>
+      <c r="AS27" s="2" t="inlineStr"/>
+      <c r="AT27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW27" s="2" t="inlineStr"/>
+      <c r="AX27" s="2" t="inlineStr"/>
+      <c r="AY27" s="2" t="inlineStr"/>
+      <c r="AZ27" s="2" t="inlineStr"/>
+      <c r="BA27" s="2" t="inlineStr"/>
+      <c r="BB27" s="2" t="inlineStr"/>
+      <c r="BC27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD27" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE27" s="2" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH27" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI27" s="2" t="inlineStr"/>
+      <c r="BJ27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr"/>
+      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BM27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:10:53</t>
+        </is>
+      </c>
+      <c r="BN27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:10:53</t>
+        </is>
+      </c>
+      <c r="BO27" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/bda17dbf386f421389ed6370f811d70d.mp3</t>
+        </is>
+      </c>
+      <c r="BP27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 4 秒 </t>
+        </is>
+      </c>
+      <c r="BQ27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:07:46</t>
+        </is>
+      </c>
+      <c r="BR27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT27" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV27" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW27" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX27" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY27" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ27" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="inlineStr"/>
+      <c r="AM28" s="2" t="inlineStr"/>
+      <c r="AN28" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO28" s="2" t="inlineStr"/>
+      <c r="AP28" s="2" t="inlineStr"/>
+      <c r="AQ28" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR28" s="2" t="inlineStr"/>
+      <c r="AS28" s="2" t="inlineStr"/>
+      <c r="AT28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW28" s="2" t="inlineStr"/>
+      <c r="AX28" s="2" t="inlineStr"/>
+      <c r="AY28" s="2" t="inlineStr"/>
+      <c r="AZ28" s="2" t="inlineStr"/>
+      <c r="BA28" s="2" t="inlineStr"/>
+      <c r="BB28" s="2" t="inlineStr"/>
+      <c r="BC28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD28" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE28" s="2" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH28" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BJ28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr"/>
+      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BM28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:00:43</t>
+        </is>
+      </c>
+      <c r="BN28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:00:43</t>
+        </is>
+      </c>
+      <c r="BO28" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/86b9a3463f6b40988e95832b993002f4.mp3</t>
+        </is>
+      </c>
+      <c r="BP28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 26 秒 </t>
+        </is>
+      </c>
+      <c r="BQ28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:58:14</t>
+        </is>
+      </c>
+      <c r="BR28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT28" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV28" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW28" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX28" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY28" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ28" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL29" s="2" t="inlineStr"/>
+      <c r="AM29" s="2" t="inlineStr"/>
+      <c r="AN29" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="inlineStr"/>
+      <c r="AP29" s="2" t="inlineStr"/>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR29" s="2" t="inlineStr"/>
+      <c r="AS29" s="2" t="inlineStr"/>
+      <c r="AT29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW29" s="2" t="inlineStr"/>
+      <c r="AX29" s="2" t="inlineStr"/>
+      <c r="AY29" s="2" t="inlineStr"/>
+      <c r="AZ29" s="2" t="inlineStr"/>
+      <c r="BA29" s="2" t="inlineStr"/>
+      <c r="BB29" s="2" t="inlineStr"/>
+      <c r="BC29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD29" s="2" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE29" s="2" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH29" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI29" s="2" t="inlineStr"/>
+      <c r="BJ29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr"/>
+      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BM29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:57:25</t>
+        </is>
+      </c>
+      <c r="BN29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:57:25</t>
+        </is>
+      </c>
+      <c r="BO29" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/a20165306c164ddfa57672b5816d8b5c.mp3</t>
+        </is>
+      </c>
+      <c r="BP29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 12 秒 </t>
+        </is>
+      </c>
+      <c r="BQ29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:55:09</t>
+        </is>
+      </c>
+      <c r="BR29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT29" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV29" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW29" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX29" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY29" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ29" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2次及以上</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL30" s="2" t="inlineStr"/>
+      <c r="AM30" s="2" t="inlineStr"/>
+      <c r="AN30" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AP30" s="2" t="inlineStr"/>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR30" s="2" t="inlineStr"/>
+      <c r="AS30" s="2" t="inlineStr"/>
+      <c r="AT30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU30" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW30" s="2" t="inlineStr"/>
+      <c r="AX30" s="2" t="inlineStr"/>
+      <c r="AY30" s="2" t="inlineStr"/>
+      <c r="AZ30" s="2" t="inlineStr"/>
+      <c r="BA30" s="2" t="inlineStr"/>
+      <c r="BB30" s="2" t="inlineStr"/>
+      <c r="BC30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BD30" s="2" t="inlineStr"/>
+      <c r="BE30" s="2" t="inlineStr"/>
+      <c r="BF30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH30" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BJ30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr"/>
+      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BM30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:40:49</t>
+        </is>
+      </c>
+      <c r="BN30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:40:49</t>
+        </is>
+      </c>
+      <c r="BO30" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/53b5194f2d7c4bc0ba8dd14e9afe4caa.mp3</t>
+        </is>
+      </c>
+      <c r="BP30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 49 秒 </t>
+        </is>
+      </c>
+      <c r="BQ30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:38:57</t>
+        </is>
+      </c>
+      <c r="BR30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT30" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV30" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体博览城</t>
+        </is>
+      </c>
+      <c r="BW30" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX30" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY30" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ30" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>26-35岁</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL31" s="2" t="inlineStr"/>
+      <c r="AM31" s="2" t="inlineStr"/>
+      <c r="AN31" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO31" s="2" t="inlineStr"/>
+      <c r="AP31" s="2" t="inlineStr"/>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR31" s="2" t="inlineStr"/>
+      <c r="AS31" s="2" t="inlineStr"/>
+      <c r="AT31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW31" s="2" t="inlineStr"/>
+      <c r="AX31" s="2" t="inlineStr"/>
+      <c r="AY31" s="2" t="inlineStr"/>
+      <c r="AZ31" s="2" t="inlineStr"/>
+      <c r="BA31" s="2" t="inlineStr"/>
+      <c r="BB31" s="2" t="inlineStr"/>
+      <c r="BC31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BD31" s="2" t="inlineStr"/>
+      <c r="BE31" s="2" t="inlineStr"/>
+      <c r="BF31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH31" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BJ31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr"/>
+      <c r="BL31" s="2" t="inlineStr"/>
+      <c r="BM31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:36:31</t>
+        </is>
+      </c>
+      <c r="BN31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:36:31</t>
+        </is>
+      </c>
+      <c r="BO31" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/d5ec9c3050de4f11b78de3480848d88f.mp3</t>
+        </is>
+      </c>
+      <c r="BP31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 23 秒 </t>
+        </is>
+      </c>
+      <c r="BQ31" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:35:05</t>
+        </is>
+      </c>
+      <c r="BR31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT31" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV31" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体中心国博壁球馆</t>
+        </is>
+      </c>
+      <c r="BW31" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX31" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY31" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ31" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2次及以上</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AH32" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL32" s="2" t="inlineStr"/>
+      <c r="AM32" s="2" t="inlineStr"/>
+      <c r="AN32" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AP32" s="2" t="inlineStr"/>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR32" s="2" t="inlineStr"/>
+      <c r="AS32" s="2" t="inlineStr"/>
+      <c r="AT32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AU32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW32" s="2" t="inlineStr"/>
+      <c r="AX32" s="2" t="inlineStr"/>
+      <c r="AY32" s="2" t="inlineStr"/>
+      <c r="AZ32" s="2" t="inlineStr"/>
+      <c r="BA32" s="2" t="inlineStr"/>
+      <c r="BB32" s="2" t="inlineStr"/>
+      <c r="BC32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BD32" s="2" t="inlineStr"/>
+      <c r="BE32" s="2" t="inlineStr"/>
+      <c r="BF32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH32" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BJ32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr"/>
+      <c r="BL32" s="2" t="inlineStr"/>
+      <c r="BM32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:33:55</t>
+        </is>
+      </c>
+      <c r="BN32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:33:55</t>
+        </is>
+      </c>
+      <c r="BO32" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/384cba67e55b4a6ba45ed7d200dd5945.mp3</t>
+        </is>
+      </c>
+      <c r="BP32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 38 秒 </t>
+        </is>
+      </c>
+      <c r="BQ32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:32:15</t>
+        </is>
+      </c>
+      <c r="BR32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT32" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV32" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW32" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX32" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY32" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ32" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>26-35岁</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH33" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL33" s="2" t="inlineStr"/>
+      <c r="AM33" s="2" t="inlineStr"/>
+      <c r="AN33" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO33" s="2" t="inlineStr"/>
+      <c r="AP33" s="2" t="inlineStr"/>
+      <c r="AQ33" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR33" s="2" t="inlineStr"/>
+      <c r="AS33" s="2" t="inlineStr"/>
+      <c r="AT33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW33" s="2" t="inlineStr"/>
+      <c r="AX33" s="2" t="inlineStr"/>
+      <c r="AY33" s="2" t="inlineStr"/>
+      <c r="AZ33" s="2" t="inlineStr"/>
+      <c r="BA33" s="2" t="inlineStr"/>
+      <c r="BB33" s="2" t="inlineStr"/>
+      <c r="BC33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BD33" s="2" t="inlineStr"/>
+      <c r="BE33" s="2" t="inlineStr"/>
+      <c r="BF33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH33" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BJ33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr"/>
+      <c r="BL33" s="2" t="inlineStr"/>
+      <c r="BM33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 12:30:06</t>
+        </is>
+      </c>
+      <c r="BN33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 12:30:06</t>
+        </is>
+      </c>
+      <c r="BO33" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b5f5c6a9b4f14082913aafc79904c9cd.mp3</t>
+        </is>
+      </c>
+      <c r="BP33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 51 秒 </t>
+        </is>
+      </c>
+      <c r="BQ33" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 12:28:12</t>
+        </is>
+      </c>
+      <c r="BR33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT33" s="2" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV33" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW33" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX33" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BY33" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BZ33" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2次及以上</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AH34" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AL34" s="2" t="inlineStr"/>
+      <c r="AM34" s="2" t="inlineStr"/>
+      <c r="AN34" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AP34" s="2" t="inlineStr"/>
+      <c r="AQ34" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AR34" s="2" t="inlineStr"/>
+      <c r="AS34" s="2" t="inlineStr"/>
+      <c r="AT34" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AU34" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AW34" s="2" t="inlineStr"/>
+      <c r="AX34" s="2" t="inlineStr"/>
+      <c r="AY34" s="2" t="inlineStr"/>
+      <c r="AZ34" s="2" t="inlineStr"/>
+      <c r="BA34" s="2" t="inlineStr"/>
+      <c r="BB34" s="2" t="inlineStr"/>
+      <c r="BC34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BD34" s="2" t="inlineStr"/>
+      <c r="BE34" s="2" t="inlineStr"/>
+      <c r="BF34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH34" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>空中花园标识标牌太少</t>
+        </is>
+      </c>
+      <c r="BJ34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr"/>
+      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BM34" s="2" t="inlineStr">
+        <is>
           <t>2026-06-05 12:22:25</t>
         </is>
       </c>
-      <c r="BN24" s="2" t="inlineStr">
+      <c r="BN34" s="2" t="inlineStr">
         <is>
           <t>2026-06-05 12:22:25</t>
         </is>
       </c>
-      <c r="BO24" s="2" t="inlineStr">
+      <c r="BO34" s="2" t="inlineStr">
         <is>
           <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/2297f6f26a6345d181964498cafb05f3.mp3</t>
         </is>
       </c>
-      <c r="BP24" s="2" t="inlineStr">
+      <c r="BP34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2 分 23 秒 </t>
         </is>
       </c>
-      <c r="BQ24" s="2" t="inlineStr">
+      <c r="BQ34" s="2" t="inlineStr">
         <is>
           <t>2026-06-05 12:19:59</t>
         </is>
       </c>
-      <c r="BR24" s="2" t="inlineStr">
+      <c r="BR34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BS24" s="2" t="inlineStr">
+      <c r="BS34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BT24" s="2" t="inlineStr">
+      <c r="BT34" s="2" t="inlineStr">
         <is>
           <t>0,285,290,329</t>
         </is>
       </c>
-      <c r="BU24" s="2" t="inlineStr">
+      <c r="BU34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BV24" s="2" t="inlineStr">
+      <c r="BV34" s="2" t="inlineStr">
         <is>
           <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体中心国博壁球馆</t>
         </is>
       </c>
-      <c r="BW24" s="2" t="inlineStr">
+      <c r="BW34" s="2" t="inlineStr">
         <is>
           <t>杭博访问员2</t>
         </is>
       </c>
-      <c r="BX24" s="2" t="inlineStr">
+      <c r="BX34" s="2" t="inlineStr">
         <is>
           <t>一期</t>
         </is>
       </c>
-      <c r="BY24" s="4" t="inlineStr">
+      <c r="BY34" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="BZ24" s="4" t="inlineStr">
+      <c r="BZ34" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
